--- a/artfynd/A 57580-2024 artfynd.xlsx
+++ b/artfynd/A 57580-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126247793</v>
       </c>
       <c r="B2" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126247956</v>
       </c>
       <c r="B3" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126247703</v>
+        <v>126248042</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>91607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571263</v>
+        <v>571366</v>
       </c>
       <c r="R4" t="n">
-        <v>7303447</v>
+        <v>7303320</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126248042</v>
+        <v>126248012</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
+        <v>91238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571366</v>
+        <v>571376</v>
       </c>
       <c r="R5" t="n">
-        <v>7303320</v>
+        <v>7303347</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126248012</v>
+        <v>126247703</v>
       </c>
       <c r="B6" t="n">
-        <v>91236</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571376</v>
+        <v>571263</v>
       </c>
       <c r="R6" t="n">
-        <v>7303347</v>
+        <v>7303447</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>126248370</v>
       </c>
       <c r="B7" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>126247911</v>
       </c>
       <c r="B8" t="n">
-        <v>91690</v>
+        <v>91692</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>126247902</v>
       </c>
       <c r="B10" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 57580-2024 artfynd.xlsx
+++ b/artfynd/A 57580-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126247793</v>
       </c>
       <c r="B2" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126247956</v>
       </c>
       <c r="B3" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126248042</v>
       </c>
       <c r="B4" t="n">
-        <v>91607</v>
+        <v>91611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126248012</v>
+        <v>126247703</v>
       </c>
       <c r="B5" t="n">
-        <v>91238</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571376</v>
+        <v>571263</v>
       </c>
       <c r="R5" t="n">
-        <v>7303347</v>
+        <v>7303447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126247703</v>
+        <v>126248012</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>91242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571263</v>
+        <v>571376</v>
       </c>
       <c r="R6" t="n">
-        <v>7303447</v>
+        <v>7303347</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>126248370</v>
       </c>
       <c r="B7" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>126247911</v>
       </c>
       <c r="B8" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>126248359</v>
       </c>
       <c r="B9" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>126247902</v>
       </c>
       <c r="B10" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>126247844</v>
       </c>
       <c r="B11" t="n">
-        <v>75073</v>
+        <v>75077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 57580-2024 artfynd.xlsx
+++ b/artfynd/A 57580-2024 artfynd.xlsx
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126248042</v>
+        <v>126248012</v>
       </c>
       <c r="B4" t="n">
-        <v>91611</v>
+        <v>91242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571366</v>
+        <v>571376</v>
       </c>
       <c r="R4" t="n">
-        <v>7303320</v>
+        <v>7303347</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126247703</v>
+        <v>126248042</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>91611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571263</v>
+        <v>571366</v>
       </c>
       <c r="R5" t="n">
-        <v>7303447</v>
+        <v>7303320</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126248012</v>
+        <v>126247703</v>
       </c>
       <c r="B6" t="n">
-        <v>91242</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571376</v>
+        <v>571263</v>
       </c>
       <c r="R6" t="n">
-        <v>7303347</v>
+        <v>7303447</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 57580-2024 artfynd.xlsx
+++ b/artfynd/A 57580-2024 artfynd.xlsx
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126248012</v>
+        <v>126248042</v>
       </c>
       <c r="B4" t="n">
-        <v>91242</v>
+        <v>91611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1506</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571376</v>
+        <v>571366</v>
       </c>
       <c r="R4" t="n">
-        <v>7303347</v>
+        <v>7303320</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126248042</v>
+        <v>126248012</v>
       </c>
       <c r="B5" t="n">
-        <v>91611</v>
+        <v>91242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571366</v>
+        <v>571376</v>
       </c>
       <c r="R5" t="n">
-        <v>7303320</v>
+        <v>7303347</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>126248370</v>
       </c>
       <c r="B7" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57580-2024 artfynd.xlsx
+++ b/artfynd/A 57580-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126247793</v>
       </c>
       <c r="B2" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126247956</v>
       </c>
       <c r="B3" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126248042</v>
+        <v>126248012</v>
       </c>
       <c r="B4" t="n">
-        <v>91611</v>
+        <v>91245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571366</v>
+        <v>571376</v>
       </c>
       <c r="R4" t="n">
-        <v>7303320</v>
+        <v>7303347</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126248012</v>
+        <v>126247703</v>
       </c>
       <c r="B5" t="n">
-        <v>91242</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571376</v>
+        <v>571263</v>
       </c>
       <c r="R5" t="n">
-        <v>7303347</v>
+        <v>7303447</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,32 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126247703</v>
+        <v>126248042</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>91614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571263</v>
+        <v>571366</v>
       </c>
       <c r="R6" t="n">
-        <v>7303447</v>
+        <v>7303320</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>126248370</v>
       </c>
       <c r="B7" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>126247911</v>
       </c>
       <c r="B8" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>126248359</v>
       </c>
       <c r="B9" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>126247902</v>
       </c>
       <c r="B10" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>126247844</v>
       </c>
       <c r="B11" t="n">
-        <v>75077</v>
+        <v>75080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 57580-2024 artfynd.xlsx
+++ b/artfynd/A 57580-2024 artfynd.xlsx
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126247703</v>
+        <v>126248042</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>91614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571263</v>
+        <v>571366</v>
       </c>
       <c r="R5" t="n">
-        <v>7303447</v>
+        <v>7303320</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,32 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126248042</v>
+        <v>126247703</v>
       </c>
       <c r="B6" t="n">
-        <v>91614</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571366</v>
+        <v>571263</v>
       </c>
       <c r="R6" t="n">
-        <v>7303320</v>
+        <v>7303447</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 57580-2024 artfynd.xlsx
+++ b/artfynd/A 57580-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126247793</v>
+        <v>126248370</v>
       </c>
       <c r="B2" t="n">
-        <v>91263</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571263</v>
+        <v>571509</v>
       </c>
       <c r="R2" t="n">
-        <v>7303442</v>
+        <v>7302872</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Bördig och frodig grannaturskog med stora mängder död ved</t>
+          <t>Storblockig barrblandskog med naturskogskaraktär</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126247956</v>
+        <v>126247902</v>
       </c>
       <c r="B3" t="n">
-        <v>91263</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571346</v>
+        <v>571325</v>
       </c>
       <c r="R3" t="n">
-        <v>7303353</v>
+        <v>7303389</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>126248012</v>
       </c>
       <c r="B4" t="n">
-        <v>91245</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126248042</v>
+        <v>126247911</v>
       </c>
       <c r="B5" t="n">
-        <v>91614</v>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1506</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571366</v>
+        <v>571325</v>
       </c>
       <c r="R5" t="n">
-        <v>7303320</v>
+        <v>7303389</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126247703</v>
+        <v>126247844</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>83312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571263</v>
+        <v>571283</v>
       </c>
       <c r="R6" t="n">
-        <v>7303447</v>
+        <v>7303409</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,32 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126248370</v>
+        <v>126248042</v>
       </c>
       <c r="B7" t="n">
-        <v>96614</v>
+        <v>92292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>1506</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571509</v>
+        <v>571366</v>
       </c>
       <c r="R7" t="n">
-        <v>7302872</v>
+        <v>7303320</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Storblockig barrblandskog med naturskogskaraktär</t>
+          <t>Bördig och frodig grannaturskog med stora mängder död ved</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1287,45 +1287,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126247911</v>
+        <v>126248359</v>
       </c>
       <c r="B8" t="n">
-        <v>91699</v>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blekselet, Blekselet, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571325</v>
+        <v>571520</v>
       </c>
       <c r="R8" t="n">
-        <v>7303389</v>
+        <v>7302870</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,12 +1369,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Bördig och frodig grannaturskog med stora mängder död ved</t>
+          <t>Storblockig barrblandskog med naturskogskaraktär</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1389,48 +1393,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126248359</v>
+        <v>126247703</v>
       </c>
       <c r="B9" t="n">
-        <v>80084</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blekselet, Blekselet, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571520</v>
+        <v>571263</v>
       </c>
       <c r="R9" t="n">
-        <v>7302870</v>
+        <v>7303447</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,13 +1472,12 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Storblockig barrblandskog med naturskogskaraktär</t>
+          <t>Bördig och frodig grannaturskog med stora mängder död ved</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1492,210 +1492,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>126247902</v>
-      </c>
-      <c r="B10" t="n">
-        <v>91245</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Blekselet, Blekselet, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>571325</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7303389</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Bördig och frodig grannaturskog med stora mängder död ved</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>126247844</v>
-      </c>
-      <c r="B11" t="n">
-        <v>75080</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Rödbrun blekspik</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Sclerophora coniophaea</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Blekselet, Blekselet, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>571283</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7303409</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Bördig och frodig grannaturskog med stora mängder död ved</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57580-2024 artfynd.xlsx
+++ b/artfynd/A 57580-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126248370</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126248359</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126247902</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126248012</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126247911</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126247844</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126248042</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,8 +1532,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126247703</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>